--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="53">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -97,79 +97,79 @@
     <t>Gourmet</t>
   </si>
   <si>
-    <t>14.87%</t>
+    <t>24.57%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
   </si>
   <si>
-    <t>97.16%</t>
+    <t>97.67%</t>
   </si>
   <si>
     <t>Lateral Preferente Tercera Base</t>
   </si>
   <si>
-    <t>96.64%</t>
+    <t>97.42%</t>
   </si>
   <si>
     <t>Lateral Primera Base</t>
   </si>
   <si>
-    <t>80.61%</t>
+    <t>84.96%</t>
   </si>
   <si>
     <t>Lateral Tercera Base</t>
   </si>
   <si>
-    <t>48.43%</t>
+    <t>56.62%</t>
   </si>
   <si>
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>57.62%</t>
+    <t>60.87%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>33.36%</t>
+    <t>39.91%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>22.15%</t>
+    <t>28.58%</t>
   </si>
   <si>
     <t>Planta Baja</t>
   </si>
   <si>
-    <t>97.20%</t>
+    <t>97.49%</t>
   </si>
   <si>
     <t>Premier 1ra-3ra</t>
   </si>
   <si>
-    <t>93.97%</t>
+    <t>96.99%</t>
   </si>
   <si>
     <t>Premier Home</t>
   </si>
   <si>
-    <t>99.43%</t>
+    <t>99.62%</t>
   </si>
   <si>
     <t>SUITES</t>
   </si>
   <si>
-    <t>4.42%</t>
+    <t>7.53%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>60.84%</t>
+    <t>64.96%</t>
   </si>
 </sst>
 </file>
@@ -812,7 +812,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="7">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>23</v>
@@ -854,10 +854,10 @@
         <v>639</v>
       </c>
       <c r="Q8" s="7">
-        <v>95</v>
+        <v>157</v>
       </c>
       <c r="R8" s="7">
-        <v>544</v>
+        <v>482</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>28</v>
@@ -871,7 +871,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="7">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="7">
         <v>23</v>
@@ -913,10 +913,10 @@
         <v>387</v>
       </c>
       <c r="Q9" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="R9" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S9" s="8" t="s">
         <v>30</v>
@@ -930,7 +930,7 @@
         <v>23</v>
       </c>
       <c r="C10" s="7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D10" s="7">
         <v>21</v>
@@ -972,10 +972,10 @@
         <v>387</v>
       </c>
       <c r="Q10" s="7">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="R10" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S10" s="8" t="s">
         <v>32</v>
@@ -989,7 +989,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="7">
-        <v>559</v>
+        <v>616</v>
       </c>
       <c r="D11" s="7">
         <v>84</v>
@@ -1031,10 +1031,10 @@
         <v>1310</v>
       </c>
       <c r="Q11" s="7">
-        <v>1056</v>
+        <v>1113</v>
       </c>
       <c r="R11" s="7">
-        <v>254</v>
+        <v>197</v>
       </c>
       <c r="S11" s="8" t="s">
         <v>34</v>
@@ -1048,7 +1048,7 @@
         <v>23</v>
       </c>
       <c r="C12" s="7">
-        <v>301</v>
+        <v>413</v>
       </c>
       <c r="D12" s="7">
         <v>43</v>
@@ -1084,16 +1084,16 @@
         <v>23</v>
       </c>
       <c r="O12" s="7">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="P12" s="7">
         <v>1307</v>
       </c>
       <c r="Q12" s="7">
-        <v>633</v>
+        <v>740</v>
       </c>
       <c r="R12" s="7">
-        <v>674</v>
+        <v>567</v>
       </c>
       <c r="S12" s="8" t="s">
         <v>36</v>
@@ -1107,7 +1107,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="7">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="D13" s="7">
         <v>86</v>
@@ -1149,10 +1149,10 @@
         <v>1444</v>
       </c>
       <c r="Q13" s="7">
-        <v>832</v>
+        <v>879</v>
       </c>
       <c r="R13" s="7">
-        <v>612</v>
+        <v>565</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>38</v>
@@ -1162,11 +1162,11 @@
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>23</v>
+      <c r="B14" s="7">
+        <v>4</v>
       </c>
       <c r="C14" s="7">
-        <v>299</v>
+        <v>365</v>
       </c>
       <c r="D14" s="7">
         <v>57</v>
@@ -1208,10 +1208,10 @@
         <v>1070</v>
       </c>
       <c r="Q14" s="7">
-        <v>357</v>
+        <v>427</v>
       </c>
       <c r="R14" s="7">
-        <v>713</v>
+        <v>643</v>
       </c>
       <c r="S14" s="8" t="s">
         <v>40</v>
@@ -1225,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="7">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D15" s="7">
         <v>25</v>
@@ -1267,10 +1267,10 @@
         <v>1088</v>
       </c>
       <c r="Q15" s="7">
-        <v>241</v>
+        <v>311</v>
       </c>
       <c r="R15" s="7">
-        <v>847</v>
+        <v>777</v>
       </c>
       <c r="S15" s="8" t="s">
         <v>42</v>
@@ -1284,13 +1284,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="7">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="D16" s="7">
         <v>119</v>
       </c>
       <c r="E16" s="7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>23</v>
@@ -1320,16 +1320,16 @@
         <v>23</v>
       </c>
       <c r="O16" s="7">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="P16" s="7">
         <v>1036</v>
       </c>
       <c r="Q16" s="7">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="R16" s="7">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S16" s="8" t="s">
         <v>44</v>
@@ -1343,7 +1343,7 @@
         <v>23</v>
       </c>
       <c r="C17" s="7">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="D17" s="7">
         <v>107</v>
@@ -1385,10 +1385,10 @@
         <v>896</v>
       </c>
       <c r="Q17" s="7">
-        <v>842</v>
+        <v>869</v>
       </c>
       <c r="R17" s="7">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="S17" s="8" t="s">
         <v>46</v>
@@ -1402,7 +1402,7 @@
         <v>23</v>
       </c>
       <c r="C18" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D18" s="7">
         <v>45</v>
@@ -1444,10 +1444,10 @@
         <v>530</v>
       </c>
       <c r="Q18" s="7">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="R18" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S18" s="8" t="s">
         <v>48</v>
@@ -1482,7 +1482,7 @@
         <v>23</v>
       </c>
       <c r="J19" s="7">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>23</v>
@@ -1503,10 +1503,10 @@
         <v>770</v>
       </c>
       <c r="Q19" s="7">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="R19" s="7">
-        <v>736</v>
+        <v>712</v>
       </c>
       <c r="S19" s="8" t="s">
         <v>50</v>

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="53">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -85,73 +85,73 @@
     <t>-</t>
   </si>
   <si>
-    <t>99.04%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Butaca Preferente Tercera Base</t>
   </si>
   <si>
-    <t>98.39%</t>
+    <t>99.68%</t>
   </si>
   <si>
     <t>Gourmet</t>
   </si>
   <si>
-    <t>24.57%</t>
+    <t>35.21%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
   </si>
   <si>
+    <t>98.45%</t>
+  </si>
+  <si>
+    <t>Lateral Preferente Tercera Base</t>
+  </si>
+  <si>
     <t>97.67%</t>
   </si>
   <si>
-    <t>Lateral Preferente Tercera Base</t>
-  </si>
-  <si>
-    <t>97.42%</t>
-  </si>
-  <si>
     <t>Lateral Primera Base</t>
   </si>
   <si>
-    <t>84.96%</t>
+    <t>94.58%</t>
   </si>
   <si>
     <t>Lateral Tercera Base</t>
   </si>
   <si>
-    <t>56.62%</t>
+    <t>79.95%</t>
   </si>
   <si>
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>60.87%</t>
+    <t>73.75%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>39.91%</t>
+    <t>53.18%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>28.58%</t>
+    <t>41.91%</t>
   </si>
   <si>
     <t>Planta Baja</t>
   </si>
   <si>
-    <t>97.49%</t>
+    <t>98.55%</t>
   </si>
   <si>
     <t>Premier 1ra-3ra</t>
   </si>
   <si>
-    <t>96.99%</t>
+    <t>99.11%</t>
   </si>
   <si>
     <t>Premier Home</t>
@@ -163,13 +163,13 @@
     <t>SUITES</t>
   </si>
   <si>
-    <t>7.53%</t>
+    <t>25.97%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>64.96%</t>
+    <t>75.01%</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="7">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D6" s="7">
         <v>16</v>
@@ -714,8 +714,8 @@
       <c r="I6" s="7">
         <v>140</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>23</v>
+      <c r="J6" s="7">
+        <v>62</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -730,16 +730,16 @@
         <v>23</v>
       </c>
       <c r="O6" s="7">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="P6" s="7">
         <v>311</v>
       </c>
       <c r="Q6" s="7">
-        <v>308</v>
-      </c>
-      <c r="R6" s="7">
-        <v>3</v>
+        <v>311</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="S6" s="8" t="s">
         <v>24</v>
@@ -753,7 +753,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="7">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D7" s="7">
         <v>35</v>
@@ -773,8 +773,8 @@
       <c r="I7" s="7">
         <v>50</v>
       </c>
-      <c r="J7" s="7" t="s">
-        <v>23</v>
+      <c r="J7" s="7">
+        <v>54</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>23</v>
@@ -789,16 +789,16 @@
         <v>23</v>
       </c>
       <c r="O7" s="7">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="P7" s="7">
         <v>311</v>
       </c>
       <c r="Q7" s="7">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="R7" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S7" s="8" t="s">
         <v>26</v>
@@ -812,7 +812,7 @@
         <v>23</v>
       </c>
       <c r="C8" s="7">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>23</v>
@@ -832,8 +832,8 @@
       <c r="I8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="7" t="s">
-        <v>23</v>
+      <c r="J8" s="7">
+        <v>24</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>23</v>
@@ -854,10 +854,10 @@
         <v>639</v>
       </c>
       <c r="Q8" s="7">
-        <v>157</v>
+        <v>225</v>
       </c>
       <c r="R8" s="7">
-        <v>482</v>
+        <v>414</v>
       </c>
       <c r="S8" s="8" t="s">
         <v>28</v>
@@ -871,7 +871,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="7">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" s="7">
         <v>23</v>
@@ -891,8 +891,8 @@
       <c r="I9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J9" s="7" t="s">
-        <v>23</v>
+      <c r="J9" s="7">
+        <v>131</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>23</v>
@@ -907,16 +907,16 @@
         <v>23</v>
       </c>
       <c r="O9" s="7">
-        <v>155</v>
+        <v>24</v>
       </c>
       <c r="P9" s="7">
         <v>387</v>
       </c>
       <c r="Q9" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="R9" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="S9" s="8" t="s">
         <v>30</v>
@@ -950,8 +950,8 @@
       <c r="I10" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>23</v>
+      <c r="J10" s="7">
+        <v>152</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>23</v>
@@ -966,16 +966,16 @@
         <v>23</v>
       </c>
       <c r="O10" s="7">
-        <v>181</v>
+        <v>30</v>
       </c>
       <c r="P10" s="7">
         <v>387</v>
       </c>
       <c r="Q10" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="R10" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S10" s="8" t="s">
         <v>32</v>
@@ -989,7 +989,7 @@
         <v>23</v>
       </c>
       <c r="C11" s="7">
-        <v>616</v>
+        <v>712</v>
       </c>
       <c r="D11" s="7">
         <v>84</v>
@@ -1009,8 +1009,8 @@
       <c r="I11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="7" t="s">
-        <v>23</v>
+      <c r="J11" s="7">
+        <v>210</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>23</v>
@@ -1025,16 +1025,16 @@
         <v>23</v>
       </c>
       <c r="O11" s="7">
-        <v>373</v>
+        <v>193</v>
       </c>
       <c r="P11" s="7">
         <v>1310</v>
       </c>
       <c r="Q11" s="7">
-        <v>1113</v>
+        <v>1239</v>
       </c>
       <c r="R11" s="7">
-        <v>197</v>
+        <v>71</v>
       </c>
       <c r="S11" s="8" t="s">
         <v>34</v>
@@ -1044,11 +1044,11 @@
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>23</v>
+      <c r="B12" s="7">
+        <v>10</v>
       </c>
       <c r="C12" s="7">
-        <v>413</v>
+        <v>651</v>
       </c>
       <c r="D12" s="7">
         <v>43</v>
@@ -1068,8 +1068,8 @@
       <c r="I12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="7" t="s">
-        <v>23</v>
+      <c r="J12" s="7">
+        <v>220</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>23</v>
@@ -1084,16 +1084,16 @@
         <v>23</v>
       </c>
       <c r="O12" s="7">
-        <v>276</v>
+        <v>113</v>
       </c>
       <c r="P12" s="7">
         <v>1307</v>
       </c>
       <c r="Q12" s="7">
-        <v>740</v>
+        <v>1045</v>
       </c>
       <c r="R12" s="7">
-        <v>567</v>
+        <v>262</v>
       </c>
       <c r="S12" s="8" t="s">
         <v>36</v>
@@ -1107,7 +1107,7 @@
         <v>23</v>
       </c>
       <c r="C13" s="7">
-        <v>601</v>
+        <v>787</v>
       </c>
       <c r="D13" s="7">
         <v>86</v>
@@ -1149,10 +1149,10 @@
         <v>1444</v>
       </c>
       <c r="Q13" s="7">
-        <v>879</v>
+        <v>1065</v>
       </c>
       <c r="R13" s="7">
-        <v>565</v>
+        <v>379</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>38</v>
@@ -1162,11 +1162,11 @@
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="7">
-        <v>4</v>
+      <c r="B14" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="C14" s="7">
-        <v>365</v>
+        <v>511</v>
       </c>
       <c r="D14" s="7">
         <v>57</v>
@@ -1208,10 +1208,10 @@
         <v>1070</v>
       </c>
       <c r="Q14" s="7">
-        <v>427</v>
+        <v>569</v>
       </c>
       <c r="R14" s="7">
-        <v>643</v>
+        <v>501</v>
       </c>
       <c r="S14" s="8" t="s">
         <v>40</v>
@@ -1225,7 +1225,7 @@
         <v>23</v>
       </c>
       <c r="C15" s="7">
-        <v>282</v>
+        <v>427</v>
       </c>
       <c r="D15" s="7">
         <v>25</v>
@@ -1267,10 +1267,10 @@
         <v>1088</v>
       </c>
       <c r="Q15" s="7">
-        <v>311</v>
+        <v>456</v>
       </c>
       <c r="R15" s="7">
-        <v>777</v>
+        <v>632</v>
       </c>
       <c r="S15" s="8" t="s">
         <v>42</v>
@@ -1284,7 +1284,7 @@
         <v>23</v>
       </c>
       <c r="C16" s="7">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="D16" s="7">
         <v>119</v>
@@ -1320,16 +1320,16 @@
         <v>23</v>
       </c>
       <c r="O16" s="7">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="P16" s="7">
         <v>1036</v>
       </c>
       <c r="Q16" s="7">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="R16" s="7">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="S16" s="8" t="s">
         <v>44</v>
@@ -1343,13 +1343,13 @@
         <v>23</v>
       </c>
       <c r="C17" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="D17" s="7">
         <v>107</v>
       </c>
       <c r="E17" s="7">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>23</v>
@@ -1364,7 +1364,7 @@
         <v>23</v>
       </c>
       <c r="J17" s="7">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>23</v>
@@ -1379,16 +1379,16 @@
         <v>23</v>
       </c>
       <c r="O17" s="7">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="P17" s="7">
         <v>896</v>
       </c>
       <c r="Q17" s="7">
-        <v>869</v>
+        <v>888</v>
       </c>
       <c r="R17" s="7">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="S17" s="8" t="s">
         <v>46</v>
@@ -1422,8 +1422,8 @@
       <c r="I18" s="7">
         <v>14</v>
       </c>
-      <c r="J18" s="7" t="s">
-        <v>23</v>
+      <c r="J18" s="7">
+        <v>113</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>23</v>
@@ -1438,7 +1438,7 @@
         <v>23</v>
       </c>
       <c r="O18" s="7">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="P18" s="7">
         <v>530</v>
@@ -1482,7 +1482,7 @@
         <v>23</v>
       </c>
       <c r="J19" s="7">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>23</v>
@@ -1503,10 +1503,10 @@
         <v>770</v>
       </c>
       <c r="Q19" s="7">
-        <v>58</v>
+        <v>200</v>
       </c>
       <c r="R19" s="7">
-        <v>712</v>
+        <v>570</v>
       </c>
       <c r="S19" s="8" t="s">
         <v>50</v>

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>6.04%</t>
+    <t>11.35%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -94,103 +94,91 @@
     <t>Butaca Preferente Tercera Base</t>
   </si>
   <si>
-    <t>99.68%</t>
-  </si>
-  <si>
     <t>Gourmet</t>
   </si>
   <si>
-    <t>41.78%</t>
+    <t>44.99%</t>
   </si>
   <si>
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>0.65%</t>
+    <t>4.42%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>11.32%</t>
+    <t>40.14%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>0.60%</t>
+    <t>1.45%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
   </si>
   <si>
+    <t>Lateral Preferente Tercera Base</t>
+  </si>
+  <si>
     <t>98.45%</t>
   </si>
   <si>
-    <t>Lateral Preferente Tercera Base</t>
-  </si>
-  <si>
-    <t>98.19%</t>
-  </si>
-  <si>
     <t>Lateral Primera Base</t>
   </si>
   <si>
-    <t>94.66%</t>
+    <t>96.64%</t>
   </si>
   <si>
     <t>Lateral Tercera Base</t>
   </si>
   <si>
-    <t>87.76%</t>
+    <t>95.56%</t>
   </si>
   <si>
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>79.50%</t>
+    <t>85.25%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>58.60%</t>
+    <t>69.91%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>51.93%</t>
+    <t>64.52%</t>
   </si>
   <si>
     <t>Planta Baja</t>
   </si>
   <si>
-    <t>98.26%</t>
-  </si>
-  <si>
     <t>Premier 1ra-3ra</t>
   </si>
   <si>
-    <t>99.44%</t>
+    <t>99.89%</t>
   </si>
   <si>
     <t>Premier Home</t>
   </si>
   <si>
-    <t>99.25%</t>
-  </si>
-  <si>
     <t>SUITES</t>
   </si>
   <si>
-    <t>25.97%</t>
+    <t>28.31%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.27%</t>
+    <t>66.40%</t>
   </si>
 </sst>
 </file>
@@ -703,7 +691,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -738,14 +726,14 @@
       <c r="N6" s="6">
         <v>2</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="Q6" s="6">
-        <v>389</v>
+        <v>367</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -848,30 +836,30 @@
         <v>22</v>
       </c>
       <c r="N8" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>310</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>1</v>
+        <v>311</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
-        <v>639</v>
+        <v>749</v>
       </c>
       <c r="C9" s="6">
-        <v>198</v>
+        <v>268</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -910,24 +898,24 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>267</v>
+        <v>337</v>
       </c>
       <c r="Q9" s="6">
-        <v>372</v>
+        <v>412</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -966,24 +954,24 @@
         <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="Q10" s="6">
-        <v>1215</v>
+        <v>1169</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -1015,31 +1003,31 @@
       <c r="M11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>22</v>
+      <c r="N11" s="6">
+        <v>107</v>
       </c>
       <c r="O11" s="6">
         <v>4</v>
       </c>
       <c r="P11" s="6">
-        <v>66</v>
+        <v>234</v>
       </c>
       <c r="Q11" s="6">
-        <v>517</v>
+        <v>349</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1078,24 +1066,24 @@
         <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="6">
-        <v>1168</v>
+        <v>1158</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6">
         <v>387</v>
       </c>
       <c r="C13" s="6">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" s="6">
         <v>23</v>
@@ -1128,24 +1116,24 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P13" s="6">
-        <v>381</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>6</v>
+        <v>387</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B14" s="6">
         <v>387</v>
@@ -1184,36 +1172,36 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q14" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6">
         <v>1310</v>
       </c>
       <c r="C15" s="6">
-        <v>763</v>
+        <v>847</v>
       </c>
       <c r="D15" s="6">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E15" s="6">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>22</v>
@@ -1240,36 +1228,36 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>1240</v>
+        <v>1266</v>
       </c>
       <c r="Q15" s="6">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" s="6">
         <v>1307</v>
       </c>
       <c r="C16" s="6">
-        <v>761</v>
+        <v>881</v>
       </c>
       <c r="D16" s="6">
         <v>43</v>
       </c>
       <c r="E16" s="6">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1284,7 +1272,7 @@
         <v>22</v>
       </c>
       <c r="J16" s="6">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="K16" s="6" t="s">
         <v>22</v>
@@ -1296,30 +1284,30 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="O16" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P16" s="6">
-        <v>1147</v>
+        <v>1249</v>
       </c>
       <c r="Q16" s="6">
-        <v>160</v>
+        <v>58</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B17" s="6">
         <v>1444</v>
       </c>
       <c r="C17" s="6">
-        <v>866</v>
+        <v>951</v>
       </c>
       <c r="D17" s="6">
         <v>86</v>
@@ -1355,27 +1343,27 @@
         <v>182</v>
       </c>
       <c r="O17" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P17" s="6">
-        <v>1148</v>
+        <v>1231</v>
       </c>
       <c r="Q17" s="6">
-        <v>296</v>
+        <v>213</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6">
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>563</v>
+        <v>681</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1411,27 +1399,27 @@
         <v>5</v>
       </c>
       <c r="O18" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P18" s="6">
-        <v>627</v>
+        <v>748</v>
       </c>
       <c r="Q18" s="6">
-        <v>443</v>
+        <v>322</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="6">
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>536</v>
+        <v>669</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1466,43 +1454,43 @@
       <c r="N19" s="6">
         <v>4</v>
       </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+      <c r="O19" s="6">
+        <v>4</v>
       </c>
       <c r="P19" s="6">
-        <v>565</v>
+        <v>702</v>
       </c>
       <c r="Q19" s="6">
-        <v>523</v>
+        <v>386</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="6">
         <v>1036</v>
       </c>
       <c r="C20" s="6">
-        <v>672</v>
+        <v>690</v>
       </c>
       <c r="D20" s="6">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" s="6">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G20" s="6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H20" s="6">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I20" s="6">
         <v>12</v>
@@ -1520,30 +1508,30 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>77</v>
-      </c>
-      <c r="O20" s="6">
-        <v>2</v>
+        <v>69</v>
+      </c>
+      <c r="O20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>1018</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>18</v>
+        <v>1036</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B21" s="6">
         <v>896</v>
       </c>
       <c r="C21" s="6">
-        <v>568</v>
+        <v>573</v>
       </c>
       <c r="D21" s="6">
         <v>107</v>
@@ -1578,28 +1566,28 @@
       <c r="N21" s="6">
         <v>53</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P21" s="6">
+        <v>895</v>
+      </c>
+      <c r="Q21" s="6">
         <v>1</v>
       </c>
-      <c r="P21" s="6">
-        <v>891</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>5</v>
-      </c>
       <c r="R21" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B22" s="6">
         <v>530</v>
       </c>
       <c r="C22" s="6">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D22" s="6">
         <v>45</v>
@@ -1632,24 +1620,24 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>526</v>
-      </c>
-      <c r="Q22" s="6">
-        <v>4</v>
+        <v>530</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6">
         <v>770</v>
@@ -1660,8 +1648,8 @@
       <c r="D23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E23" s="6" t="s">
-        <v>22</v>
+      <c r="E23" s="6">
+        <v>18</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
@@ -1694,18 +1682,18 @@
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="Q23" s="6">
-        <v>570</v>
+        <v>552</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1756,7 +1744,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="54">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>11.35%</t>
+    <t>21.01%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -97,25 +97,25 @@
     <t>Gourmet</t>
   </si>
   <si>
-    <t>44.99%</t>
+    <t>56.21%</t>
   </si>
   <si>
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>4.42%</t>
+    <t>32.87%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>40.14%</t>
+    <t>74.27%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>1.45%</t>
+    <t>6.47%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
@@ -124,37 +124,34 @@
     <t>Lateral Preferente Tercera Base</t>
   </si>
   <si>
-    <t>98.45%</t>
-  </si>
-  <si>
     <t>Lateral Primera Base</t>
   </si>
   <si>
-    <t>96.64%</t>
+    <t>96.95%</t>
   </si>
   <si>
     <t>Lateral Tercera Base</t>
   </si>
   <si>
-    <t>95.56%</t>
+    <t>97.09%</t>
   </si>
   <si>
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>85.25%</t>
+    <t>86.22%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>69.91%</t>
+    <t>79.07%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>64.52%</t>
+    <t>72.15%</t>
   </si>
   <si>
     <t>Planta Baja</t>
@@ -163,9 +160,6 @@
     <t>Premier 1ra-3ra</t>
   </si>
   <si>
-    <t>99.89%</t>
-  </si>
-  <si>
     <t>Premier Home</t>
   </si>
   <si>
@@ -178,7 +172,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>66.40%</t>
+    <t>72.78%</t>
   </si>
 </sst>
 </file>
@@ -691,7 +685,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -727,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="O6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P6" s="6">
-        <v>47</v>
+        <v>87</v>
       </c>
       <c r="Q6" s="6">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -859,7 +853,7 @@
         <v>749</v>
       </c>
       <c r="C9" s="6">
-        <v>268</v>
+        <v>352</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -898,10 +892,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>337</v>
+        <v>421</v>
       </c>
       <c r="Q9" s="6">
-        <v>412</v>
+        <v>328</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -915,13 +909,13 @@
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>54</v>
+        <v>157</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>22</v>
+      <c r="E10" s="6">
+        <v>240</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -950,14 +944,14 @@
       <c r="N10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>22</v>
+      <c r="O10" s="6">
+        <v>5</v>
       </c>
       <c r="P10" s="6">
-        <v>54</v>
+        <v>402</v>
       </c>
       <c r="Q10" s="6">
-        <v>1169</v>
+        <v>821</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -971,16 +965,16 @@
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>123</v>
+        <v>292</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>22</v>
+      <c r="E11" s="6">
+        <v>21</v>
+      </c>
+      <c r="F11" s="6">
+        <v>40</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>22</v>
@@ -1004,16 +998,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="O11" s="6">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="P11" s="6">
-        <v>234</v>
+        <v>433</v>
       </c>
       <c r="Q11" s="6">
-        <v>349</v>
+        <v>150</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -1027,13 +1021,13 @@
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>22</v>
+      <c r="E12" s="6">
+        <v>20</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1062,14 +1056,14 @@
       <c r="N12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
+      <c r="O12" s="6">
+        <v>7</v>
       </c>
       <c r="P12" s="6">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="Q12" s="6">
-        <v>1158</v>
+        <v>1099</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1089,7 +1083,7 @@
         <v>23</v>
       </c>
       <c r="E13" s="6">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1116,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1139,7 +1133,7 @@
         <v>387</v>
       </c>
       <c r="C14" s="6">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D14" s="6">
         <v>21</v>
@@ -1172,36 +1166,36 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>381</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>6</v>
+        <v>387</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6">
         <v>1310</v>
       </c>
       <c r="C15" s="6">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="D15" s="6">
         <v>88</v>
       </c>
       <c r="E15" s="6">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>22</v>
@@ -1228,36 +1222,36 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>1266</v>
+        <v>1270</v>
       </c>
       <c r="Q15" s="6">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6">
         <v>1307</v>
       </c>
       <c r="C16" s="6">
-        <v>881</v>
+        <v>906</v>
       </c>
       <c r="D16" s="6">
         <v>43</v>
       </c>
       <c r="E16" s="6">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1284,30 +1278,30 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>44</v>
-      </c>
-      <c r="O16" s="6">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>1249</v>
+        <v>1269</v>
       </c>
       <c r="Q16" s="6">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="6">
         <v>1444</v>
       </c>
       <c r="C17" s="6">
-        <v>951</v>
+        <v>967</v>
       </c>
       <c r="D17" s="6">
         <v>86</v>
@@ -1342,28 +1336,28 @@
       <c r="N17" s="6">
         <v>182</v>
       </c>
-      <c r="O17" s="6">
-        <v>2</v>
+      <c r="O17" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1231</v>
+        <v>1245</v>
       </c>
       <c r="Q17" s="6">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B18" s="6">
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>681</v>
+        <v>752</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1396,30 +1390,30 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="O18" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P18" s="6">
-        <v>748</v>
+        <v>846</v>
       </c>
       <c r="Q18" s="6">
-        <v>322</v>
+        <v>224</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6">
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>669</v>
+        <v>742</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1452,24 +1446,24 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="O19" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P19" s="6">
-        <v>702</v>
+        <v>785</v>
       </c>
       <c r="Q19" s="6">
-        <v>386</v>
+        <v>303</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B20" s="6">
         <v>1036</v>
@@ -1525,7 +1519,7 @@
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B21" s="6">
         <v>896</v>
@@ -1564,30 +1558,30 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P21" s="6">
-        <v>895</v>
-      </c>
-      <c r="Q21" s="6">
-        <v>1</v>
+        <v>896</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="6">
         <v>530</v>
       </c>
       <c r="C22" s="6">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="D22" s="6">
         <v>45</v>
@@ -1620,7 +1614,7 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
@@ -1637,7 +1631,7 @@
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="6">
         <v>770</v>
@@ -1688,12 +1682,12 @@
         <v>552</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1744,7 +1738,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="54">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>21.01%</t>
+    <t>25.12%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -97,25 +97,25 @@
     <t>Gourmet</t>
   </si>
   <si>
-    <t>56.21%</t>
+    <t>56.74%</t>
   </si>
   <si>
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>32.87%</t>
+    <t>42.60%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>74.27%</t>
+    <t>85.08%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>6.47%</t>
+    <t>9.45%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
@@ -145,13 +145,13 @@
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>79.07%</t>
+    <t>84.39%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>72.15%</t>
+    <t>76.84%</t>
   </si>
   <si>
     <t>Planta Baja</t>
@@ -172,7 +172,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>72.78%</t>
+    <t>75.09%</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -721,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="O6" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P6" s="6">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="Q6" s="6">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -853,7 +853,7 @@
         <v>749</v>
       </c>
       <c r="C9" s="6">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -892,10 +892,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="Q9" s="6">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -909,7 +909,7 @@
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>157</v>
+        <v>274</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -945,13 +945,13 @@
         <v>22</v>
       </c>
       <c r="O10" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P10" s="6">
-        <v>402</v>
+        <v>521</v>
       </c>
       <c r="Q10" s="6">
-        <v>821</v>
+        <v>702</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -965,7 +965,7 @@
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>292</v>
+        <v>364</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -998,16 +998,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O11" s="6">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="P11" s="6">
-        <v>433</v>
+        <v>496</v>
       </c>
       <c r="Q11" s="6">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -1021,7 +1021,7 @@
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1056,14 +1056,14 @@
       <c r="N12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="6">
-        <v>7</v>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="Q12" s="6">
-        <v>1099</v>
+        <v>1064</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1251,7 +1251,7 @@
         <v>43</v>
       </c>
       <c r="E16" s="6">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1278,7 +1278,7 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
@@ -1357,7 +1357,7 @@
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>752</v>
+        <v>806</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1390,16 +1390,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>31</v>
-      </c>
-      <c r="O18" s="6">
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>846</v>
+        <v>903</v>
       </c>
       <c r="Q18" s="6">
-        <v>224</v>
+        <v>167</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>44</v>
@@ -1413,7 +1413,7 @@
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>742</v>
+        <v>785</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1446,16 +1446,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>16</v>
-      </c>
-      <c r="O19" s="6">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>785</v>
+        <v>836</v>
       </c>
       <c r="Q19" s="6">
-        <v>303</v>
+        <v>252</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>46</v>

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="54">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>25.12%</t>
+    <t>37.44%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -97,25 +97,25 @@
     <t>Gourmet</t>
   </si>
   <si>
-    <t>56.74%</t>
+    <t>58.34%</t>
   </si>
   <si>
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>42.60%</t>
+    <t>50.12%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>85.08%</t>
+    <t>94.51%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>9.45%</t>
+    <t>14.04%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
@@ -127,31 +127,31 @@
     <t>Lateral Primera Base</t>
   </si>
   <si>
-    <t>96.95%</t>
+    <t>97.40%</t>
   </si>
   <si>
     <t>Lateral Tercera Base</t>
   </si>
   <si>
-    <t>97.09%</t>
+    <t>97.25%</t>
   </si>
   <si>
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>86.22%</t>
+    <t>87.33%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>84.39%</t>
+    <t>89.16%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>76.84%</t>
+    <t>83.73%</t>
   </si>
   <si>
     <t>Planta Baja</t>
@@ -172,7 +172,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>75.09%</t>
+    <t>77.85%</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -721,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="O6" s="6">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="P6" s="6">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="Q6" s="6">
-        <v>310</v>
+        <v>259</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -853,7 +853,7 @@
         <v>749</v>
       </c>
       <c r="C9" s="6">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -892,10 +892,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="Q9" s="6">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -909,13 +909,13 @@
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>274</v>
+        <v>350</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -948,10 +948,10 @@
         <v>7</v>
       </c>
       <c r="P10" s="6">
-        <v>521</v>
+        <v>613</v>
       </c>
       <c r="Q10" s="6">
-        <v>702</v>
+        <v>610</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -965,7 +965,7 @@
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>364</v>
+        <v>418</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -998,16 +998,16 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O11" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P11" s="6">
-        <v>496</v>
+        <v>551</v>
       </c>
       <c r="Q11" s="6">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -1021,7 +1021,7 @@
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
@@ -1056,14 +1056,14 @@
       <c r="N12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>22</v>
+      <c r="O12" s="6">
+        <v>8</v>
       </c>
       <c r="P12" s="6">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="Q12" s="6">
-        <v>1064</v>
+        <v>1010</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1189,7 +1189,7 @@
         <v>1310</v>
       </c>
       <c r="C15" s="6">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="D15" s="6">
         <v>88</v>
@@ -1222,16 +1222,16 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="Q15" s="6">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>38</v>
@@ -1245,13 +1245,13 @@
         <v>1307</v>
       </c>
       <c r="C16" s="6">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D16" s="6">
         <v>43</v>
       </c>
       <c r="E16" s="6">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1278,16 +1278,16 @@
         <v>22</v>
       </c>
       <c r="N16" s="6">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="Q16" s="6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>40</v>
@@ -1301,13 +1301,13 @@
         <v>1444</v>
       </c>
       <c r="C17" s="6">
-        <v>967</v>
+        <v>993</v>
       </c>
       <c r="D17" s="6">
         <v>86</v>
       </c>
       <c r="E17" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1334,16 +1334,16 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1245</v>
+        <v>1261</v>
       </c>
       <c r="Q17" s="6">
-        <v>199</v>
+        <v>183</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>42</v>
@@ -1357,7 +1357,7 @@
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1390,16 +1390,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>40</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>22</v>
+        <v>42</v>
+      </c>
+      <c r="O18" s="6">
+        <v>8</v>
       </c>
       <c r="P18" s="6">
-        <v>903</v>
+        <v>954</v>
       </c>
       <c r="Q18" s="6">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>44</v>
@@ -1413,7 +1413,7 @@
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>785</v>
+        <v>829</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1430,8 +1430,8 @@
       <c r="H19" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="6" t="s">
-        <v>22</v>
+      <c r="I19" s="6">
+        <v>4</v>
       </c>
       <c r="J19" s="6" t="s">
         <v>22</v>
@@ -1446,16 +1446,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>26</v>
-      </c>
-      <c r="O19" s="6" t="s">
-        <v>22</v>
+        <v>34</v>
+      </c>
+      <c r="O19" s="6">
+        <v>19</v>
       </c>
       <c r="P19" s="6">
-        <v>836</v>
+        <v>911</v>
       </c>
       <c r="Q19" s="6">
-        <v>252</v>
+        <v>177</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>46</v>
@@ -1587,10 +1587,10 @@
         <v>45</v>
       </c>
       <c r="E22" s="6">
-        <v>5</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="F22" s="6">
+        <v>6</v>
       </c>
       <c r="G22" s="6">
         <v>21</v>
@@ -1602,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="J22" s="6">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>22</v>
@@ -1614,7 +1614,7 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="54">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>37.44%</t>
+    <t>53.86%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -103,19 +103,19 @@
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>50.12%</t>
+    <t>75.39%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>94.51%</t>
+    <t>98.63%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>14.04%</t>
+    <t>28.09%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
@@ -139,19 +139,19 @@
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>87.33%</t>
+    <t>89.20%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>89.16%</t>
+    <t>98.60%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>83.73%</t>
+    <t>93.84%</t>
   </si>
   <si>
     <t>Planta Baja</t>
@@ -166,13 +166,13 @@
     <t>SUITES</t>
   </si>
   <si>
-    <t>28.31%</t>
+    <t>30.13%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>77.85%</t>
+    <t>83.30%</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>127</v>
+        <v>217</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -721,13 +721,13 @@
         <v>2</v>
       </c>
       <c r="O6" s="6">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>155</v>
+        <v>223</v>
       </c>
       <c r="Q6" s="6">
-        <v>259</v>
+        <v>191</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -746,8 +746,8 @@
       <c r="D7" s="6">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -774,7 +774,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -909,13 +909,13 @@
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>350</v>
+        <v>542</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>256</v>
+        <v>371</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -941,17 +941,17 @@
       <c r="M10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N10" s="6" t="s">
-        <v>22</v>
+      <c r="N10" s="6">
+        <v>2</v>
       </c>
       <c r="O10" s="6">
         <v>7</v>
       </c>
       <c r="P10" s="6">
-        <v>613</v>
+        <v>922</v>
       </c>
       <c r="Q10" s="6">
-        <v>610</v>
+        <v>301</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -965,7 +965,7 @@
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -1000,14 +1000,14 @@
       <c r="N11" s="6">
         <v>70</v>
       </c>
-      <c r="O11" s="6">
-        <v>2</v>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>551</v>
+        <v>575</v>
       </c>
       <c r="Q11" s="6">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -1021,13 +1021,13 @@
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>137</v>
+        <v>288</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1057,13 +1057,13 @@
         <v>22</v>
       </c>
       <c r="O12" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="P12" s="6">
-        <v>165</v>
+        <v>330</v>
       </c>
       <c r="Q12" s="6">
-        <v>1010</v>
+        <v>845</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1083,7 +1083,7 @@
         <v>23</v>
       </c>
       <c r="E13" s="6">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1110,7 +1110,7 @@
         <v>22</v>
       </c>
       <c r="N13" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>22</v>
@@ -1189,7 +1189,7 @@
         <v>1310</v>
       </c>
       <c r="C15" s="6">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="D15" s="6">
         <v>88</v>
@@ -1222,7 +1222,7 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
@@ -1301,13 +1301,13 @@
         <v>1444</v>
       </c>
       <c r="C17" s="6">
-        <v>993</v>
+        <v>1013</v>
       </c>
       <c r="D17" s="6">
         <v>86</v>
       </c>
       <c r="E17" s="6">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>22</v>
@@ -1334,16 +1334,16 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1261</v>
+        <v>1288</v>
       </c>
       <c r="Q17" s="6">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>42</v>
@@ -1357,7 +1357,7 @@
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>847</v>
+        <v>955</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1393,13 +1393,13 @@
         <v>42</v>
       </c>
       <c r="O18" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="P18" s="6">
-        <v>954</v>
+        <v>1055</v>
       </c>
       <c r="Q18" s="6">
-        <v>116</v>
+        <v>15</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>44</v>
@@ -1413,7 +1413,7 @@
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>829</v>
+        <v>957</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1449,13 +1449,13 @@
         <v>34</v>
       </c>
       <c r="O19" s="6">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="P19" s="6">
-        <v>911</v>
+        <v>1021</v>
       </c>
       <c r="Q19" s="6">
-        <v>177</v>
+        <v>67</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>46</v>
@@ -1546,7 +1546,7 @@
         <v>22</v>
       </c>
       <c r="J21" s="6">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K21" s="6" t="s">
         <v>22</v>
@@ -1558,7 +1558,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
@@ -1581,13 +1581,13 @@
         <v>530</v>
       </c>
       <c r="C22" s="6">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D22" s="6">
         <v>45</v>
       </c>
       <c r="E22" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F22" s="6">
         <v>6</v>
@@ -1602,7 +1602,7 @@
         <v>14</v>
       </c>
       <c r="J22" s="6">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>22</v>
@@ -1614,7 +1614,7 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
@@ -1643,7 +1643,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="6">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
@@ -1676,10 +1676,10 @@
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>218</v>
+        <v>232</v>
       </c>
       <c r="Q23" s="6">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>51</v>

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="54">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>53.86%</t>
+    <t>82.37%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -97,25 +97,25 @@
     <t>Gourmet</t>
   </si>
   <si>
-    <t>58.34%</t>
+    <t>71.03%</t>
   </si>
   <si>
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>75.39%</t>
+    <t>99.26%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>98.63%</t>
+    <t>98.97%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>28.09%</t>
+    <t>67.15%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
@@ -127,19 +127,19 @@
     <t>Lateral Primera Base</t>
   </si>
   <si>
+    <t>97.71%</t>
+  </si>
+  <si>
+    <t>Lateral Tercera Base</t>
+  </si>
+  <si>
     <t>97.40%</t>
   </si>
   <si>
-    <t>Lateral Tercera Base</t>
-  </si>
-  <si>
-    <t>97.25%</t>
-  </si>
-  <si>
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>89.20%</t>
+    <t>91.55%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
@@ -151,7 +151,7 @@
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>93.84%</t>
+    <t>96.97%</t>
   </si>
   <si>
     <t>Planta Baja</t>
@@ -166,13 +166,13 @@
     <t>SUITES</t>
   </si>
   <si>
-    <t>30.13%</t>
+    <t>45.84%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>83.30%</t>
+    <t>91.05%</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>217</v>
+        <v>339</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -720,14 +720,14 @@
       <c r="N6" s="6">
         <v>2</v>
       </c>
-      <c r="O6" s="6">
-        <v>4</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>223</v>
+        <v>341</v>
       </c>
       <c r="Q6" s="6">
-        <v>191</v>
+        <v>73</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -746,8 +746,8 @@
       <c r="D7" s="6">
         <v>16</v>
       </c>
-      <c r="E7" s="6">
-        <v>2</v>
+      <c r="E7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -774,7 +774,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -853,7 +853,7 @@
         <v>749</v>
       </c>
       <c r="C9" s="6">
-        <v>368</v>
+        <v>463</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -892,10 +892,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>437</v>
+        <v>532</v>
       </c>
       <c r="Q9" s="6">
-        <v>312</v>
+        <v>217</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -909,13 +909,13 @@
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>542</v>
+        <v>779</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="6">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>22</v>
@@ -942,16 +942,16 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="O10" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P10" s="6">
-        <v>922</v>
+        <v>1214</v>
       </c>
       <c r="Q10" s="6">
-        <v>301</v>
+        <v>9</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>30</v>
@@ -965,7 +965,7 @@
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -1004,10 +1004,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="Q11" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>
@@ -1021,13 +1021,13 @@
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>288</v>
+        <v>718</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1053,17 +1053,17 @@
       <c r="M12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="6" t="s">
-        <v>22</v>
+      <c r="N12" s="6">
+        <v>1</v>
       </c>
       <c r="O12" s="6">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="P12" s="6">
-        <v>330</v>
+        <v>789</v>
       </c>
       <c r="Q12" s="6">
-        <v>845</v>
+        <v>386</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>34</v>
@@ -1139,7 +1139,7 @@
         <v>21</v>
       </c>
       <c r="E14" s="6">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1166,7 +1166,7 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
@@ -1189,13 +1189,13 @@
         <v>1310</v>
       </c>
       <c r="C15" s="6">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D15" s="6">
         <v>88</v>
       </c>
       <c r="E15" s="6">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>22</v>
@@ -1228,10 +1228,10 @@
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="Q15" s="6">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>38</v>
@@ -1245,13 +1245,13 @@
         <v>1307</v>
       </c>
       <c r="C16" s="6">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="D16" s="6">
         <v>43</v>
       </c>
       <c r="E16" s="6">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>22</v>
@@ -1284,10 +1284,10 @@
         <v>22</v>
       </c>
       <c r="P16" s="6">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="Q16" s="6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>40</v>
@@ -1301,7 +1301,7 @@
         <v>1444</v>
       </c>
       <c r="C17" s="6">
-        <v>1013</v>
+        <v>1048</v>
       </c>
       <c r="D17" s="6">
         <v>86</v>
@@ -1334,16 +1334,16 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1288</v>
+        <v>1322</v>
       </c>
       <c r="Q17" s="6">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>42</v>
@@ -1357,7 +1357,7 @@
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1392,8 +1392,8 @@
       <c r="N18" s="6">
         <v>42</v>
       </c>
-      <c r="O18" s="6">
-        <v>1</v>
+      <c r="O18" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P18" s="6">
         <v>1055</v>
@@ -1413,7 +1413,7 @@
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>957</v>
+        <v>992</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1448,14 +1448,14 @@
       <c r="N19" s="6">
         <v>34</v>
       </c>
-      <c r="O19" s="6">
-        <v>1</v>
+      <c r="O19" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1021</v>
+        <v>1055</v>
       </c>
       <c r="Q19" s="6">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>46</v>
@@ -1475,7 +1475,7 @@
         <v>120</v>
       </c>
       <c r="E20" s="6">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>22</v>
@@ -1502,7 +1502,7 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
@@ -1525,13 +1525,13 @@
         <v>896</v>
       </c>
       <c r="C21" s="6">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D21" s="6">
         <v>107</v>
       </c>
       <c r="E21" s="6">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>22</v>
@@ -1558,7 +1558,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
@@ -1587,7 +1587,7 @@
         <v>45</v>
       </c>
       <c r="E22" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F22" s="6">
         <v>6</v>
@@ -1614,7 +1614,7 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
@@ -1643,7 +1643,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="6">
-        <v>32</v>
+        <v>153</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
@@ -1676,10 +1676,10 @@
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>232</v>
+        <v>353</v>
       </c>
       <c r="Q23" s="6">
-        <v>538</v>
+        <v>417</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>51</v>

--- a/data/asistencia/Charros 2026.xlsx
+++ b/data/asistencia/Charros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="56">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>82.37%</t>
+    <t>93.96%</t>
   </si>
   <si>
     <t>Butaca Preferente Primera Base</t>
@@ -97,25 +97,22 @@
     <t>Gourmet</t>
   </si>
   <si>
-    <t>71.03%</t>
+    <t>70.23%</t>
   </si>
   <si>
     <t>Lateral Alta Primera Base</t>
   </si>
   <si>
-    <t>99.26%</t>
-  </si>
-  <si>
     <t>Lateral Preferente Alta</t>
   </si>
   <si>
-    <t>98.97%</t>
+    <t>99.31%</t>
   </si>
   <si>
     <t>Lateral Preferente Alta Tercera Base</t>
   </si>
   <si>
-    <t>67.15%</t>
+    <t>93.87%</t>
   </si>
   <si>
     <t>Lateral Preferente Primera Base</t>
@@ -124,10 +121,13 @@
     <t>Lateral Preferente Tercera Base</t>
   </si>
   <si>
+    <t>99.74%</t>
+  </si>
+  <si>
     <t>Lateral Primera Base</t>
   </si>
   <si>
-    <t>97.71%</t>
+    <t>98.17%</t>
   </si>
   <si>
     <t>Lateral Tercera Base</t>
@@ -139,40 +139,46 @@
     <t>Planta Alta Central</t>
   </si>
   <si>
-    <t>91.55%</t>
+    <t>96.61%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Primera Base</t>
   </si>
   <si>
-    <t>98.60%</t>
+    <t>98.88%</t>
   </si>
   <si>
     <t>Planta Alta Lateral Tercera Base</t>
   </si>
   <si>
-    <t>96.97%</t>
+    <t>98.16%</t>
   </si>
   <si>
     <t>Planta Baja</t>
   </si>
   <si>
+    <t>99.90%</t>
+  </si>
+  <si>
     <t>Premier 1ra-3ra</t>
   </si>
   <si>
     <t>Premier Home</t>
   </si>
   <si>
+    <t>99.62%</t>
+  </si>
+  <si>
     <t>SUITES</t>
   </si>
   <si>
-    <t>45.84%</t>
+    <t>48.96%</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>91.05%</t>
+    <t>94.26%</t>
   </si>
 </sst>
 </file>
@@ -685,7 +691,7 @@
         <v>414</v>
       </c>
       <c r="C6" s="6">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -717,17 +723,17 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6">
-        <v>2</v>
+      <c r="N6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="Q6" s="6">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -741,7 +747,7 @@
         <v>311</v>
       </c>
       <c r="C7" s="6">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D7" s="6">
         <v>16</v>
@@ -774,7 +780,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -853,7 +859,7 @@
         <v>749</v>
       </c>
       <c r="C9" s="6">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -892,10 +898,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="Q9" s="6">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -909,7 +915,7 @@
         <v>1223</v>
       </c>
       <c r="C10" s="6">
-        <v>779</v>
+        <v>797</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>22</v>
@@ -942,30 +948,30 @@
         <v>22</v>
       </c>
       <c r="N10" s="6">
-        <v>24</v>
-      </c>
-      <c r="O10" s="6">
-        <v>6</v>
+        <v>21</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P10" s="6">
-        <v>1214</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>9</v>
+        <v>1223</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6">
         <v>583</v>
       </c>
       <c r="C11" s="6">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -998,36 +1004,36 @@
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="Q11" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>1175</v>
       </c>
       <c r="C12" s="6">
-        <v>718</v>
+        <v>1046</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E12" s="6">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>22</v>
@@ -1053,25 +1059,25 @@
       <c r="M12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N12" s="6">
-        <v>1</v>
-      </c>
-      <c r="O12" s="6">
-        <v>18</v>
+      <c r="N12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P12" s="6">
-        <v>789</v>
+        <v>1103</v>
       </c>
       <c r="Q12" s="6">
-        <v>386</v>
+        <v>72</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>387</v>
@@ -1127,19 +1133,19 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="6">
         <v>387</v>
       </c>
       <c r="C14" s="6">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="D14" s="6">
         <v>21</v>
       </c>
       <c r="E14" s="6">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>22</v>
@@ -1166,19 +1172,19 @@
         <v>22</v>
       </c>
       <c r="N14" s="6">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P14" s="6">
-        <v>387</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>22</v>
+        <v>386</v>
+      </c>
+      <c r="Q14" s="6">
+        <v>1</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
@@ -1189,7 +1195,7 @@
         <v>1310</v>
       </c>
       <c r="C15" s="6">
-        <v>872</v>
+        <v>877</v>
       </c>
       <c r="D15" s="6">
         <v>88</v>
@@ -1222,16 +1228,16 @@
         <v>22</v>
       </c>
       <c r="N15" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P15" s="6">
-        <v>1280</v>
+        <v>1286</v>
       </c>
       <c r="Q15" s="6">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>38</v>
@@ -1245,7 +1251,7 @@
         <v>1307</v>
       </c>
       <c r="C16" s="6">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="D16" s="6">
         <v>43</v>
@@ -1277,8 +1283,8 @@
       <c r="M16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="6">
-        <v>3</v>
+      <c r="N16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>22</v>
@@ -1301,7 +1307,7 @@
         <v>1444</v>
       </c>
       <c r="C17" s="6">
-        <v>1048</v>
+        <v>1124</v>
       </c>
       <c r="D17" s="6">
         <v>86</v>
@@ -1334,16 +1340,16 @@
         <v>22</v>
       </c>
       <c r="N17" s="6">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P17" s="6">
-        <v>1322</v>
+        <v>1395</v>
       </c>
       <c r="Q17" s="6">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>42</v>
@@ -1357,7 +1363,7 @@
         <v>1070</v>
       </c>
       <c r="C18" s="6">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="D18" s="6">
         <v>57</v>
@@ -1390,16 +1396,16 @@
         <v>22</v>
       </c>
       <c r="N18" s="6">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P18" s="6">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="Q18" s="6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>44</v>
@@ -1413,7 +1419,7 @@
         <v>1088</v>
       </c>
       <c r="C19" s="6">
-        <v>992</v>
+        <v>1007</v>
       </c>
       <c r="D19" s="6">
         <v>25</v>
@@ -1446,16 +1452,16 @@
         <v>22</v>
       </c>
       <c r="N19" s="6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P19" s="6">
-        <v>1055</v>
+        <v>1068</v>
       </c>
       <c r="Q19" s="6">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>46</v>
@@ -1469,7 +1475,7 @@
         <v>1036</v>
       </c>
       <c r="C20" s="6">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="D20" s="6">
         <v>120</v>
@@ -1502,30 +1508,30 @@
         <v>22</v>
       </c>
       <c r="N20" s="6">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P20" s="6">
-        <v>1036</v>
-      </c>
-      <c r="Q20" s="6" t="s">
-        <v>22</v>
+        <v>1035</v>
+      </c>
+      <c r="Q20" s="6">
+        <v>1</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B21" s="6">
         <v>896</v>
       </c>
       <c r="C21" s="6">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D21" s="6">
         <v>107</v>
@@ -1558,7 +1564,7 @@
         <v>22</v>
       </c>
       <c r="N21" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>22</v>
@@ -1575,19 +1581,19 @@
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6">
         <v>530</v>
       </c>
       <c r="C22" s="6">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D22" s="6">
         <v>45</v>
       </c>
       <c r="E22" s="6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F22" s="6">
         <v>6</v>
@@ -1614,24 +1620,24 @@
         <v>22</v>
       </c>
       <c r="N22" s="6">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>22</v>
       </c>
       <c r="P22" s="6">
-        <v>530</v>
-      </c>
-      <c r="Q22" s="6" t="s">
-        <v>22</v>
+        <v>528</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>2</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6">
         <v>770</v>
@@ -1643,7 +1649,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="6">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>22</v>
@@ -1676,18 +1682,18 @@
         <v>22</v>
       </c>
       <c r="P23" s="6">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="Q23" s="6">
-        <v>417</v>
+        <v>393</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B24" s="7">
         <f>SUM(B6:B23)</f>
@@ -1738,7 +1744,7 @@
         <f>SUM(Q6:Q23)</f>
       </c>
       <c r="R24" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
